--- a/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
+++ b/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:T127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -585,6 +595,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UGEL CASTILLA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -663,6 +683,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -741,6 +771,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -819,6 +859,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -897,6 +947,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -975,6 +1035,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1053,6 +1123,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1131,6 +1211,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UGEL CASTILLA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1209,6 +1299,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1287,6 +1387,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1371,6 +1481,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1459,6 +1579,16 @@
           <t>080606</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1547,6 +1677,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1635,6 +1775,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1723,6 +1873,16 @@
           <t>101006</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1811,6 +1971,16 @@
           <t>130107</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1899,6 +2069,16 @@
           <t>130107</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1985,6 +2165,16 @@
           <t>150119</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2071,6 +2261,16 @@
           <t>150129</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2155,6 +2355,16 @@
           <t>160604</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>UGEL UCAYALI-CONTAMANA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2243,6 +2453,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2331,6 +2551,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2419,6 +2649,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2507,6 +2747,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2595,6 +2845,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2683,6 +2943,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2763,6 +3033,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2851,6 +3131,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2939,6 +3229,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3019,6 +3319,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3107,6 +3417,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3195,6 +3515,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3283,6 +3613,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3363,6 +3703,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3443,6 +3793,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3531,6 +3891,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3611,6 +3981,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3691,6 +4071,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3771,6 +4161,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3851,6 +4251,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3931,6 +4341,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4009,6 +4429,16 @@
       <c r="R43" t="inlineStr">
         <is>
           <t>170302</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
     </row>
@@ -4083,6 +4513,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4163,6 +4603,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4251,6 +4701,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4339,6 +4799,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4427,6 +4897,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4515,6 +4995,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4603,6 +5093,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4683,6 +5183,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4771,6 +5281,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4851,6 +5371,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4939,6 +5469,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5027,6 +5567,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5107,6 +5657,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5187,6 +5747,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5267,6 +5837,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5347,6 +5927,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5435,6 +6025,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5515,6 +6115,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5603,6 +6213,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5683,6 +6303,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5763,6 +6393,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5843,6 +6483,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5931,6 +6581,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6011,6 +6671,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6091,6 +6761,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6171,6 +6851,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6251,6 +6941,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6331,6 +7031,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6411,6 +7121,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6499,6 +7219,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6579,6 +7309,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6667,6 +7407,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6755,6 +7505,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6843,6 +7603,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6923,6 +7693,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7011,6 +7791,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7091,6 +7881,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7179,6 +7979,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7267,6 +8077,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7355,6 +8175,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7443,6 +8273,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7523,6 +8363,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7611,6 +8461,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7691,6 +8551,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7779,6 +8649,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7867,6 +8747,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7955,6 +8845,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8043,6 +8943,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8131,6 +9041,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8211,6 +9131,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8299,6 +9229,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8379,6 +9319,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8459,6 +9409,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8539,6 +9499,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8619,6 +9589,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8699,6 +9679,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8779,6 +9769,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8859,6 +9859,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8947,6 +9957,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9027,6 +10047,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9115,6 +10145,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9203,6 +10243,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9291,6 +10341,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9379,6 +10439,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9467,6 +10537,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9555,6 +10635,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9635,6 +10725,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9715,6 +10815,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9795,6 +10905,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9875,6 +10995,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9963,6 +11093,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10051,6 +11191,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10139,6 +11289,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10227,6 +11387,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10315,6 +11485,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10403,6 +11583,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10491,6 +11681,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -10579,6 +11779,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10659,6 +11869,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10747,6 +11967,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -10835,6 +12065,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10919,6 +12159,16 @@
           <t>230105</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11001,6 +12251,16 @@
       <c r="R126" t="inlineStr">
         <is>
           <t>230105</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -11081,6 +12341,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
+++ b/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T127"/>
+  <dimension ref="A1:U127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -605,6 +610,11 @@
           <t>UGEL CASTILLA</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -693,6 +703,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -781,6 +796,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -869,6 +889,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -957,6 +982,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1045,6 +1075,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1133,6 +1168,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1221,6 +1261,11 @@
           <t>UGEL CASTILLA</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1309,6 +1354,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1397,6 +1447,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cayarani</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1491,6 +1546,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1589,6 +1649,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Pablo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1687,6 +1752,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1785,6 +1855,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1883,6 +1958,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Francisco de Asis</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1981,6 +2061,11 @@
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Moche</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2079,6 +2164,11 @@
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Moche</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2175,6 +2265,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2271,6 +2366,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2365,6 +2465,11 @@
           <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pampa Hermosa</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2463,6 +2568,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2561,6 +2671,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2659,6 +2774,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2757,6 +2877,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2855,6 +2980,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2953,6 +3083,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3043,6 +3178,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3141,6 +3281,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3239,6 +3384,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3329,6 +3479,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3427,6 +3582,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3525,6 +3685,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3623,6 +3788,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3713,6 +3883,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3803,6 +3978,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3901,6 +4081,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3991,6 +4176,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4081,6 +4271,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4171,6 +4366,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4261,6 +4461,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4351,6 +4556,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4441,6 +4651,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4523,6 +4738,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4613,6 +4833,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4711,6 +4936,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4809,6 +5039,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4907,6 +5142,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5005,6 +5245,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5103,6 +5348,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5193,6 +5443,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5291,6 +5546,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5381,6 +5641,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5479,6 +5744,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5577,6 +5847,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5667,6 +5942,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5757,6 +6037,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5847,6 +6132,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5937,6 +6227,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6035,6 +6330,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6125,6 +6425,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6223,6 +6528,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6313,6 +6623,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6403,6 +6718,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6493,6 +6813,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6591,6 +6916,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6681,6 +7011,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6771,6 +7106,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6861,6 +7201,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6951,6 +7296,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7041,6 +7391,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7131,6 +7486,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7229,6 +7589,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7319,6 +7684,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7417,6 +7787,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7515,6 +7890,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7613,6 +7993,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7703,6 +8088,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7801,6 +8191,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7891,6 +8286,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7989,6 +8389,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8087,6 +8492,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8185,6 +8595,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8283,6 +8698,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8373,6 +8793,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8471,6 +8896,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8561,6 +8991,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8659,6 +9094,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8757,6 +9197,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8855,6 +9300,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8953,6 +9403,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9051,6 +9506,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9141,6 +9601,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9239,6 +9704,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9329,6 +9799,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9419,6 +9894,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9509,6 +9989,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9599,6 +10084,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9689,6 +10179,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9779,6 +10274,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9869,6 +10369,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9967,6 +10472,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10057,6 +10567,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10155,6 +10670,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10253,6 +10773,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10351,6 +10876,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10449,6 +10979,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10547,6 +11082,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10645,6 +11185,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10735,6 +11280,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10825,6 +11375,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10915,6 +11470,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11005,6 +11565,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11103,6 +11668,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11201,6 +11771,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11299,6 +11874,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11397,6 +11977,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -11495,6 +12080,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -11593,6 +12183,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -11691,6 +12286,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11789,6 +12389,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11879,6 +12484,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -11977,6 +12587,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12075,6 +12690,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12169,6 +12789,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12263,6 +12888,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12349,6 +12979,11 @@
       <c r="T127" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
+++ b/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U127"/>
+  <dimension ref="A1:W127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -612,6 +622,16 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>40459 SAN ROQUE/40459 SAN ROQUE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -705,6 +725,16 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>40444</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -798,6 +828,16 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>ARCATA/40568/40568</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -891,6 +931,16 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>CHOCÑIHUAQUI/40577/40577</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -984,6 +1034,16 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>40592</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -1077,6 +1137,16 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>40613</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -1170,6 +1240,16 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>CAYARANI</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -1263,6 +1343,16 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>UMACHULCO</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -1356,6 +1446,16 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>CHALLA</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -1449,6 +1549,16 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>VISCA VISCA</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
       </c>
@@ -1548,6 +1658,16 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 33/FE Y ALEGRIA 33/FE Y ALEGRIA 33</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -1651,6 +1771,16 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Pablo</t>
         </is>
       </c>
@@ -1754,6 +1884,16 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>36415</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -1857,6 +1997,16 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
+          <t>36542</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -1960,6 +2110,16 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>GUZMAN SERAFICO SOTO/GUZMAN SERAFICO SOTO</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Francisco de Asis</t>
         </is>
       </c>
@@ -2063,6 +2223,16 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>1613 MI DULCE HOGAR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
       </c>
@@ -2166,6 +2336,16 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>80082 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
       </c>
@@ -2267,6 +2447,16 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>6012/6012</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -2368,6 +2558,16 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>6013 VIRGEN INMACULADA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
       </c>
@@ -2467,6 +2667,16 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>64249</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pampa Hermosa</t>
         </is>
       </c>
@@ -2570,6 +2780,16 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>345 BOCA MANU</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -2673,6 +2893,16 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -2776,6 +3006,16 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>DIAMANTE</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -2879,6 +3119,16 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
+          <t>52245</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -2982,6 +3232,16 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3085,6 +3345,16 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3180,6 +3450,16 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3283,6 +3563,16 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3386,6 +3676,16 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>50843</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3481,6 +3781,16 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3584,6 +3894,16 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
+          <t>52200</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3687,6 +4007,16 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>52133</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3790,6 +4120,16 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>CIENCIAS DE NUEVA/52159 CIENCIAS DE NUEVA</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3885,6 +4225,16 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>332 DOCE DE ENERO</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -3980,6 +4330,16 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4083,6 +4443,16 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4178,6 +4548,16 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4273,6 +4653,16 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4368,6 +4758,16 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4463,6 +4863,16 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>53004 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4558,6 +4968,16 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>EL ARCA DE PACAHUARA/52216 EL ARCA DE PACAHUARA</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4653,6 +5073,16 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4740,6 +5170,16 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4835,6 +5275,16 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -4938,6 +5388,16 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5041,6 +5501,16 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5144,6 +5614,16 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>52077/52077</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5247,6 +5727,16 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>52128</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5350,6 +5840,16 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>52129</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5445,6 +5945,16 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>440/52201</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5548,6 +6058,16 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>RICARDO PALMA SORIANO/52187 RICARDO PALMA SORIANO</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5643,6 +6163,16 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5746,6 +6276,16 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5849,6 +6389,16 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>368 NIÑOS DE LA SELVA</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -5944,6 +6494,16 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6039,6 +6599,16 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6134,6 +6704,16 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6229,6 +6809,16 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6332,6 +6922,16 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6427,6 +7027,16 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>ALTO LIBERTAD</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6530,6 +7140,16 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>NUEVA AREQUIPA</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6625,6 +7245,16 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
+          <t>376 HORMIGUITAS ESCRITORAS</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -6720,6 +7350,16 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
+          <t>52055</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -6815,6 +7455,16 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>IÑAPARI</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -6918,6 +7568,16 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -7013,6 +7673,16 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
+          <t>52062 JAVIER HERAUD/52062 JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7108,6 +7778,16 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
+          <t>52033/52033</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7203,6 +7883,16 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>52105</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7298,6 +7988,16 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>SANTO DOMINGO/SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7393,6 +8093,16 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7488,6 +8198,16 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7591,6 +8311,16 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
+          <t>52262 CARLOS MARQUEZ BRAGA</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7686,6 +8416,16 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
+          <t>SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7789,6 +8529,16 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7892,6 +8642,16 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
+          <t>JORGE CHAVEZ RENGIFO/JORGE CHAVEZ RENGIFO</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -7995,6 +8755,16 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
+          <t>HEROES DE ILLAMPU/HEROES DE ILLAMPU/HEROES DE ILLAMPU</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8090,6 +8860,16 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
+          <t>RAUL VARGAS QUIROZ/RAUL VARGAS QUIROZ</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8193,6 +8973,16 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
+          <t>52095/52095</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8288,6 +9078,16 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
+          <t>52136</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8391,6 +9191,16 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
+          <t>52242</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8494,6 +9304,16 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
+          <t>52137</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8597,6 +9417,16 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8700,6 +9530,16 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8795,6 +9635,16 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8898,6 +9748,16 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
+          <t>52081</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -8993,6 +9853,16 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9096,6 +9966,16 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
+          <t>52075</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9199,6 +10079,16 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
+          <t>52154</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9302,6 +10192,16 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
+          <t>PEDRO PAULET/PEDRO PAULET</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9405,6 +10305,16 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9508,6 +10418,16 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
+          <t>DANIEL ALCIDES CARRION/DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9603,6 +10523,16 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9706,6 +10636,16 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
+          <t>279 NIÑO DE PRAGA</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9801,6 +10741,16 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
+          <t>316 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9896,6 +10846,16 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -9991,6 +10951,16 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -10086,6 +11056,16 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -10181,6 +11161,16 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
+          <t>52061/52061</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -10276,6 +11266,16 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -10371,6 +11371,16 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -10474,6 +11484,16 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -10569,6 +11589,16 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -10672,6 +11702,16 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
+          <t>296 LAS PALMERAS</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -10775,6 +11815,16 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -10878,6 +11928,16 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -10981,6 +12041,16 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11084,6 +12154,16 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11187,6 +12267,16 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
+          <t>318 MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11282,6 +12372,16 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
+          <t>LAS ARDILLITAS</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11377,6 +12477,16 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
+          <t>LA PASTORA/LA PASTORA/LA PASTORA</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11472,6 +12582,16 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
+          <t>SAN BERNARDO/52035</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11567,6 +12687,16 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
+          <t>52084</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11670,6 +12800,16 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
+          <t>52166 NUESTRA SEÑORA DE FATIMA/52166 NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11773,6 +12913,16 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
+          <t>433 ROBERTO GUILLERMO VELA VALLES/52183/52183</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11876,6 +13026,16 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
+          <t>SANTA RITA DE CASIA</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -11979,6 +13139,16 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
+          <t>52225</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12082,6 +13252,16 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12185,6 +13365,16 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12288,6 +13478,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12391,6 +13591,16 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
+          <t>400 LUCECITAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12486,6 +13696,16 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12589,6 +13809,16 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12692,6 +13922,16 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -12791,6 +14031,16 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
+          <t>42053 BARTOLOME JULIO ROSPIGLIOSI</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -12890,6 +14140,16 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
+          <t>443 SANTA TERESITA/443 SANTA TERESITA</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -12982,6 +14242,16 @@
         </is>
       </c>
       <c r="U127" t="inlineStr">
+        <is>
+          <t>42010 SANTISIMA NIÑA MARIA/42010 SANTISIMA NIÑA MARIA</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>

--- a/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
+++ b/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
@@ -419,82 +419,82 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Provincia</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nombre de la I.E.</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tipología Completar: Total Parcial</t>
+          <t>tipologia_completar_total_parcial</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Monto incurrido en la demolición (S/)</t>
+          <t>monto_incurrido_en_la_demolicion_s</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Fecha de inicio de la actividad (o estimada)</t>
+          <t>fecha_de_inicio_de_la_actividad_o_estimada</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de culminación de la actividad (o estimada)</t>
+          <t>fecha_de_culminacion_de_la_actividad_o_estimada</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>¿La intervención resolvió la necesidad del local educativo? (Es decir, luego de la demolición parcial realizada, no se requieren demoliciones adicionales de edificaciones) (SÍ / NO)</t>
+          <t>la_intervencion_resolvio_la_necesidad_del_local_educativo_es</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>REMITENTE</t>
+          <t>remitente</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>departamento_2</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>provincia_2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>distrito_2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">

--- a/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
+++ b/output/bases_limpias/Grupo_11_DEMOLICIONES/df_anexo2_d.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W127"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,50 +484,30 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>departamento_2</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>provincia_2</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>distrito_2</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>centro_poblado</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ubigeo</t>
+          <t>area</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
-        <is>
-          <t>dre</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ugel</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>nombre_ie_2</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -587,50 +567,30 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UMACHULCO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>UMACHULCO</t>
+          <t>UGEL CASTILLA</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>UGEL CASTILLA</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>40459 SAN ROQUE/40459 SAN ROQUE</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -690,50 +650,30 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHALLA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CHALLA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>40444</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -793,50 +733,30 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ARCATA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ARCATA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>ARCATA/40568/40568</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -896,50 +816,30 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHOCÑEHUAQUE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CHOCÑEHUAQUE</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>CHOCÑIHUAQUI/40577/40577</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -999,50 +899,30 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SULPUMAYO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>SULPUMAYO</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>40592</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1102,50 +982,30 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHAIÑA</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CHAIÑA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>40613</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1205,50 +1065,30 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYARANI</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>CAYARANI</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1308,50 +1148,30 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UMACHULCO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>UMACHULCO</t>
+          <t>UGEL CASTILLA</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>UGEL CASTILLA</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>UMACHULCO</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1411,50 +1231,30 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHALLA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CHALLA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>CHALLA</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1514,50 +1314,30 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>VISCA VISCA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>VISCA VISCA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>VISCA VISCA</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1623,50 +1403,30 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>070107</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MI PERU</t>
+          <t>DRE CALLAO</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>MI PERU</t>
+          <t>UGEL VENTANILLA</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>070107</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
-        <is>
-          <t>DRE CALLAO</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>UGEL VENTANILLA</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>FE Y ALEGRIA 33/FE Y ALEGRIA 33/FE Y ALEGRIA 33</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
@@ -1736,50 +1496,30 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>SONGOÑA</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>CANCHIS</t>
+          <t>080606</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SAN PABLO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>SONGOÑA</t>
+          <t>UGEL CANCHIS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>080606</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>UGEL CANCHIS</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Pablo</t>
         </is>
@@ -1849,50 +1589,30 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCHACUAY</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>ANGARAES</t>
+          <t>090309</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>JULCAMARCA</t>
+          <t>DRE HUANCAVELICA</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ANCHACUAY</t>
+          <t>UGEL ANGARAES</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>090309</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>DRE HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>UGEL ANGARAES</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>36415</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
@@ -1962,50 +1682,30 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>MANYACCLLA</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>ANGARAES</t>
+          <t>090309</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>JULCAMARCA</t>
+          <t>DRE HUANCAVELICA</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>MANYACCLLA</t>
+          <t>UGEL ANGARAES</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>090309</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
-        <is>
-          <t>DRE HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>UGEL ANGARAES</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>36542</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
@@ -2075,50 +1775,30 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>CARAMARCA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>LAURICOCHA</t>
+          <t>101006</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>DRE HUANUCO</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CARAMARCA</t>
+          <t>UGEL LAURICOCHA</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>101006</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
-        <is>
-          <t>DRE HUANUCO</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>UGEL LAURICOCHA</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>GUZMAN SERAFICO SOTO/GUZMAN SERAFICO SOTO</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Francisco de Asis</t>
         </is>
@@ -2188,50 +1868,30 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
-        <is>
-          <t>GRE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1613 MI DULCE HOGAR</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -2301,50 +1961,30 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CURVA DE SUN</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CURVA DE SUN</t>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
-        <is>
-          <t>GRE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>80082 SAN FRANCISCO DE ASIS</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -2412,50 +2052,30 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>RINCONADA DEL PURUHUAY</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>150119</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>LURIN</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>RINCONADA DEL PURUHUAY</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>150119</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>6012/6012</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
@@ -2523,50 +2143,30 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>SAN BARTOLO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>150129</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SAN BARTOLO</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>SAN BARTOLO</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>150129</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>6013 VIRGEN INMACULADA DEL ROSARIO</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
@@ -2632,50 +2232,30 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>ALTO PERILLO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>UCAYALI</t>
+          <t>160604</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PAMPA HERMOSA</t>
+          <t>DRE LORETO</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ALTO PERILLO</t>
+          <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>160604</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
-        <is>
-          <t>DRE LORETO</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>UGEL UCAYALI-CONTAMANA</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>64249</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pampa Hermosa</t>
         </is>
@@ -2745,50 +2325,30 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BOCA DEL MANU</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>BOCA DEL MANU</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>345 BOCA MANU</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -2858,50 +2418,30 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DIAMANTE NUEVO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>DIAMANTE NUEVO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -2971,50 +2511,30 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DIAMANTE NUEVO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>DIAMANTE NUEVO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>DIAMANTE</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3084,50 +2604,30 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SARIGUEMINIKI</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>SARIGUEMINIKI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>52245</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3197,50 +2697,30 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>YOMIBATO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>YOMIBATO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3310,50 +2790,30 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TAYACOME</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>TAYACOME</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3415,50 +2875,30 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVO EDEN</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>NUEVO EDEN</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3528,50 +2968,30 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO AZUL</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PUERTO AZUL</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3641,50 +3061,30 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DIAMANTE NUEVO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>DIAMANTE NUEVO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>50843</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3746,50 +3146,30 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUENTE INAMBARI</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PUENTE INAMBARI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3859,50 +3239,30 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUENTE INAMBARI</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>PUENTE INAMBARI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>52200</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3972,50 +3332,30 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BARRANCO CHICO</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>BARRANCO CHICO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>52133</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4085,50 +3425,30 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CAYCHIHUE ALTO Y QUEBRADA NUEVA</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>CAYCHIHUE ALTO Y QUEBRADA NUEVA</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>CIENCIAS DE NUEVA/52159 CIENCIAS DE NUEVA</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4190,50 +3510,30 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>HUAYPETUE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>HUAYPETUE</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>332 DOCE DE ENERO</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4295,50 +3595,30 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO PUNKIRI</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PUERTO PUNKIRI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4408,50 +3688,30 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BARRANCO CHICO</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>BARRANCO CHICO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4513,50 +3773,30 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4618,50 +3858,30 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4723,50 +3943,30 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4828,50 +4028,30 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>53004 MIGUEL GRAU</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4933,50 +4113,30 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAHUARA</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PACAHUARA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>EL ARCA DE PACAHUARA/52216 EL ARCA DE PACAHUARA</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5038,50 +4198,30 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5135,50 +4275,30 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAHUARA</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PACAHUARA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5240,50 +4360,30 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BAMBU</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>BAMBU</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5353,50 +4453,30 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MAZUKO</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PUERTO MAZUKO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -5466,50 +4546,30 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -5579,50 +4639,30 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PALMERA</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PALMERA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>52077/52077</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -5692,50 +4732,30 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVA AREQUIPA</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NUEVA AREQUIPA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>52128</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -5805,50 +4825,30 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MAZUKO</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PUERTO MAZUKO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>52129</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -5910,50 +4910,30 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>KOTSIMBA</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>KOTSIMBA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>440/52201</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6023,50 +5003,30 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SARAYACU</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>SARAYACU</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>RICARDO PALMA SORIANO/52187 RICARDO PALMA SORIANO</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6128,50 +5088,30 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ALTO LIBERTAD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ALTO LIBERTAD</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6241,50 +5181,30 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVA AREQUIPA</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>NUEVA AREQUIPA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6354,50 +5274,30 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PONAL</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PONAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>368 NIÑOS DE LA SELVA</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6459,50 +5359,30 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>2 DE MAYO</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2 DE MAYO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6564,50 +5444,30 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CENTROMIN</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CENTROMIN</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6669,50 +5529,30 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA CANDELARIA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6774,50 +5614,30 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MAZUKO</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>MAZUKO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6887,50 +5707,30 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SOL NACIENTE</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>SOL NACIENTE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6992,50 +5792,30 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ALTO LIBERTAD</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ALTO LIBERTAD</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>ALTO LIBERTAD</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7105,50 +5885,30 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVA AREQUIPA</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>NUEVA AREQUIPA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>NUEVA AREQUIPA</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7210,50 +5970,30 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA RITA BAJA</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>SANTA RITA BAJA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>376 HORMIGUITAS ESCRITORAS</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7315,50 +6055,30 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BELGICA</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170301</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>BELGICA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>170301</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>52055</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -7420,50 +6140,30 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IÑAPARI</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170301</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>170301</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>IÑAPARI</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -7533,50 +6233,30 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BELGICA</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170301</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>BELGICA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>170301</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -7638,50 +6318,30 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LABERINTO</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>52062 JAVIER HERAUD/52062 JAVIER HERAUD</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7743,50 +6403,30 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>FLORIDA ALTA</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>FLORIDA ALTA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>52033/52033</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7848,50 +6488,30 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>FLORIDA BAJA</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>FLORIDA BAJA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>52105</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7953,50 +6573,30 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>SANTO DOMINGO/SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8058,50 +6658,30 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>AMARAKAERI</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>AMARAKAERI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8163,50 +6743,30 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LABERINTO</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>JAVIER HERAUD</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8276,50 +6836,30 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LABERINTO</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>52262 CARLOS MARQUEZ BRAGA</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8381,50 +6921,30 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8494,50 +7014,30 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PLANCHON</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PLANCHON</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8607,50 +7107,30 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PLANCHON</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PLANCHON</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>JORGE CHAVEZ RENGIFO/JORGE CHAVEZ RENGIFO</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8720,50 +7200,30 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MAVILA</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>MAVILA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>HEROES DE ILLAMPU/HEROES DE ILLAMPU/HEROES DE ILLAMPU</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8825,50 +7285,30 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ALEGRIA</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ALEGRIA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>RAUL VARGAS QUIROZ/RAUL VARGAS QUIROZ</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8938,50 +7378,30 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SUDADERO</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>SUDADERO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>52095/52095</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9043,50 +7463,30 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>FRAY MARTIN</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>FRAY MARTIN</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>52136</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9156,50 +7556,30 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO NUEVO</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PUERTO NUEVO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>52242</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9269,50 +7649,30 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TIPISHKA</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>TIPISHKA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>52137</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9382,50 +7742,30 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PLANCHON</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PLANCHON</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9495,50 +7835,30 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO LUCERNA</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PUERTO LUCERNA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9600,50 +7920,30 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ASOCIACION VILLA TERRASOL</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>ASOCIACION VILLA TERRASOL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9713,50 +8013,30 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BAJO MADRE DE DIOS</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>BAJO MADRE DE DIOS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>52081</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9818,50 +8098,30 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN JUAN GRANDE</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>SAN JUAN GRANDE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -9931,50 +8191,30 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN JOSE DE KARENE</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>SAN JOSE DE KARENE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>52075</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10044,50 +8284,30 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAL GUACAMAYO</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PACAL GUACAMAYO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>52154</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10157,50 +8377,30 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN JUAN GRANDE</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>SAN JUAN GRANDE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>PEDRO PAULET/PEDRO PAULET</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10270,50 +8470,30 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAL</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PACAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10383,50 +8563,30 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DELTA 1 / BAJO PUKIRI</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>DELTA 1 / BAJO PUKIRI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>DANIEL ALCIDES CARRION/DANIEL ALCIDES CARRION</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10488,50 +8648,30 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BOCA ISIRI</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>BOCA ISIRI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10601,50 +8741,30 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SALVACION</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>SALVACION</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>279 NIÑO DE PRAGA</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10706,50 +8826,30 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SALVACION</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>SALVACION</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>316 NIÑO JESUS</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10811,50 +8911,30 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SHIPITIARI</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>SHIPITIARI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -10916,50 +8996,30 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SALVACION</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>SALVACION</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -11021,50 +9081,30 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN LORENZO</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>SAN LORENZO</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -11126,50 +9166,30 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>52061/52061</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -11231,50 +9251,30 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -11336,50 +9336,30 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -11449,50 +9429,30 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVO PACARAN</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>NUEVO PACARAN</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -11554,50 +9514,30 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>OTILIA</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>OTILIA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11667,50 +9607,30 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>296 LAS PALMERAS</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11780,50 +9700,30 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11893,50 +9793,30 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO PARDO</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>PUERTO PARDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12006,50 +9886,30 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TRES ISLAS</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>TRES ISLAS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12119,50 +9979,30 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PALMA REAL</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>PALMA REAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12232,50 +10072,30 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>318 MI PEQUEÑO MUNDO</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12337,50 +10157,30 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>LAS ARDILLITAS</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12442,50 +10242,30 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LA PASTORA</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>LA PASTORA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>LA PASTORA/LA PASTORA/LA PASTORA</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12547,50 +10327,30 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN BERNARDO</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>SAN BERNARDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SAN BERNARDO/52035</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12652,50 +10412,30 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SONENE</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>SONENE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>52084</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12765,50 +10505,30 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BARRIO LINDO</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>BARRIO LINDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>52166 NUESTRA SEÑORA DE FATIMA/52166 NUESTRA SEÑORA DE FATIMA</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12878,50 +10598,30 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ROMPE OLAS</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>ROMPE OLAS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>433 ROBERTO GUILLERMO VELA VALLES/52183/52183</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -12991,50 +10691,30 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SANTA RITA DE CASIA</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13104,50 +10784,30 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MONTE SALVADO</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>MONTE SALVADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>52225</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13217,50 +10877,30 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CHONTA</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CHONTA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>52028</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13330,50 +10970,30 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>MIRAFLORES</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13443,50 +11063,30 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>EL CASTAÑAL</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>EL CASTAÑAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13556,50 +11156,30 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>JORGE CHAVEZ RENGIFO</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ RENGIFO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>400 LUCECITAS DEL SABER</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13661,50 +11241,30 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>JOSE ALDAMIS</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>JOSE ALDAMIS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13774,50 +11334,30 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN BERNARDO</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>SAN BERNARDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13887,50 +11427,30 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CHONTA</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>CHONTA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>52028</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -13996,50 +11516,30 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>TOMASIRI</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>230105</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>INCLAN</t>
+          <t>DRE TACNA</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>TOMASIRI</t>
+          <t>UGEL TACNA</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>230105</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
-        <is>
-          <t>DRE TACNA</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>UGEL TACNA</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>42053 BARTOLOME JULIO ROSPIGLIOSI</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -14105,50 +11605,30 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PROTER</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>230105</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>INCLAN</t>
+          <t>DRE TACNA</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PROTER</t>
+          <t>UGEL TACNA</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>230105</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
-        <is>
-          <t>DRE TACNA</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>UGEL TACNA</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>443 SANTA TERESITA/443 SANTA TERESITA</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -14213,45 +11693,25 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>230101</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>DRE TACNA</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>UGEL TACNA</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
-        <is>
-          <t>DRE TACNA</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>UGEL TACNA</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>42010 SANTISIMA NIÑA MARIA/42010 SANTISIMA NIÑA MARIA</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
